--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4689" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D85701A-637F-402D-879F-114B73D02D42}"/>
+  <xr:revisionPtr revIDLastSave="4705" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{353A9C22-61D7-9C45-B12B-02C16212F420}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -2058,7 +2058,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2309,23 +2309,36 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3320,10 +3333,6 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3645,32 +3654,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="39" customWidth="1"/>
+    <col min="1" max="1" width="24.6171875" style="101" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.58984375" style="101" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5390625" style="101" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.58984375" style="101" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" style="101" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.58984375" style="101" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.046875" style="101" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.58984375" style="101" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5078125" style="101" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.18359375" style="101" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="39.01171875" style="101" customWidth="1"/>
+    <col min="12" max="16384" width="9.14453125" style="101"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="109" t="s">
         <v>349</v>
       </c>
       <c r="C1" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="100" t="s">
+      <c r="D1" s="109" t="s">
         <v>388</v>
       </c>
       <c r="E1" s="100" t="s">
@@ -3683,740 +3693,740 @@
       <c r="H1" s="100"/>
       <c r="I1" s="100"/>
     </row>
-    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+    <row r="2" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="102" t="s">
+      <c r="B2" s="110" t="s">
         <v>350</v>
       </c>
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="102" t="s">
+      <c r="D2" s="110" t="s">
         <v>389</v>
       </c>
-      <c r="E2" s="101" t="s">
+      <c r="E2" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="102" t="s">
+      <c r="F2" s="103" t="s">
         <v>347</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="103"/>
-    </row>
-    <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="101" t="s">
+      <c r="G2" s="104"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="104"/>
+    </row>
+    <row r="3" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="102" t="s">
         <v>258</v>
       </c>
-      <c r="B3" s="102" t="s">
+      <c r="B3" s="110" t="s">
         <v>351</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="102" t="s">
+      <c r="D3" s="110" t="s">
         <v>390</v>
       </c>
-      <c r="E3" s="101" t="s">
+      <c r="E3" s="102" t="s">
         <v>311</v>
       </c>
-      <c r="F3" s="102" t="s">
+      <c r="F3" s="103" t="s">
         <v>337</v>
       </c>
-      <c r="G3" s="103"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="103"/>
-    </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="101" t="s">
+      <c r="G3" s="104"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="104"/>
+    </row>
+    <row r="4" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="110" t="s">
         <v>352</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="102" t="s">
+      <c r="D4" s="110" t="s">
         <v>336</v>
       </c>
-      <c r="E4" s="101" t="s">
+      <c r="E4" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="102" t="s">
+      <c r="F4" s="103" t="s">
         <v>338</v>
       </c>
-      <c r="G4" s="103"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="103"/>
-    </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="104" t="s">
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="104"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="110" t="s">
         <v>353</v>
       </c>
-      <c r="C5" s="101" t="s">
+      <c r="C5" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="102" t="s">
+      <c r="D5" s="110" t="s">
         <v>336</v>
       </c>
-      <c r="E5" s="101" t="s">
+      <c r="E5" s="102" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="102" t="s">
+      <c r="F5" s="103" t="s">
         <v>348</v>
       </c>
-      <c r="G5" s="103"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="103"/>
-    </row>
-    <row r="6" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="101" t="s">
+      <c r="G5" s="104"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="104"/>
+    </row>
+    <row r="6" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="110" t="s">
         <v>354</v>
       </c>
-      <c r="C6" s="101" t="s">
+      <c r="C6" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="102" t="s">
+      <c r="D6" s="110" t="s">
         <v>391</v>
       </c>
-      <c r="E6" s="101" t="s">
+      <c r="E6" s="102" t="s">
         <v>308</v>
       </c>
-      <c r="F6" s="102" t="s">
+      <c r="F6" s="103" t="s">
         <v>339</v>
       </c>
-      <c r="G6" s="103"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="103"/>
-    </row>
-    <row r="7" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="101" t="s">
+      <c r="G6" s="104"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="104"/>
+    </row>
+    <row r="7" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="110" t="s">
         <v>355</v>
       </c>
-      <c r="C7" s="101" t="s">
+      <c r="C7" s="102" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="E7" s="101" t="s">
+      <c r="E7" s="102" t="s">
         <v>300</v>
       </c>
-      <c r="F7" s="102" t="s">
+      <c r="F7" s="103" t="s">
         <v>301</v>
       </c>
-      <c r="G7" s="103"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="103"/>
-    </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="101" t="s">
+      <c r="G7" s="104"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="104"/>
+    </row>
+    <row r="8" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="110" t="s">
         <v>356</v>
       </c>
-      <c r="C8" s="101" t="s">
+      <c r="C8" s="102" t="s">
         <v>230</v>
       </c>
-      <c r="D8" s="102" t="s">
+      <c r="D8" s="110" t="s">
         <v>336</v>
       </c>
-      <c r="E8" s="101" t="s">
+      <c r="E8" s="102" t="s">
         <v>302</v>
       </c>
-      <c r="F8" s="105" t="s">
+      <c r="F8" s="108" t="s">
         <v>303</v>
       </c>
-      <c r="G8" s="103"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="103"/>
-    </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="101" t="s">
+      <c r="G8" s="104"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="104"/>
+    </row>
+    <row r="9" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="102" t="s">
         <v>314</v>
       </c>
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="110" t="s">
         <v>357</v>
       </c>
-      <c r="C9" s="101" t="s">
+      <c r="C9" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="102" t="s">
+      <c r="D9" s="110" t="s">
         <v>336</v>
       </c>
-      <c r="E9" s="101" t="s">
+      <c r="E9" s="102" t="s">
         <v>304</v>
       </c>
-      <c r="F9" s="102" t="s">
+      <c r="F9" s="103" t="s">
         <v>305</v>
       </c>
-      <c r="G9" s="103"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="103"/>
-    </row>
-    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="101" t="s">
+      <c r="G9" s="104"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="104"/>
+    </row>
+    <row r="10" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="110" t="s">
         <v>358</v>
       </c>
-      <c r="C10" s="101" t="s">
+      <c r="C10" s="102" t="s">
         <v>313</v>
       </c>
-      <c r="D10" s="102" t="s">
+      <c r="D10" s="110" t="s">
         <v>415</v>
       </c>
-      <c r="E10" s="101" t="s">
+      <c r="E10" s="102" t="s">
         <v>306</v>
       </c>
-      <c r="F10" s="102" t="s">
+      <c r="F10" s="103" t="s">
         <v>307</v>
       </c>
-      <c r="G10" s="103"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="103"/>
-    </row>
-    <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="101" t="s">
+      <c r="G10" s="104"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="104"/>
+    </row>
+    <row r="11" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="102" t="s">
         <v>265</v>
       </c>
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="110" t="s">
         <v>359</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="102" t="s">
+      <c r="D11" s="110" t="s">
         <v>416</v>
       </c>
-      <c r="E11" s="101" t="s">
+      <c r="E11" s="102" t="s">
         <v>310</v>
       </c>
-      <c r="F11" s="102" t="s">
+      <c r="F11" s="103" t="s">
         <v>309</v>
       </c>
-      <c r="G11" s="103"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="103"/>
-    </row>
-    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="101" t="s">
+      <c r="G11" s="104"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="104"/>
+    </row>
+    <row r="12" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="110" t="s">
         <v>360</v>
       </c>
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="102" t="s">
+      <c r="D12" s="110" t="s">
         <v>417</v>
       </c>
-      <c r="E12" s="101" t="s">
+      <c r="E12" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="102" t="s">
+      <c r="F12" s="103" t="s">
         <v>346</v>
       </c>
-      <c r="G12" s="103"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="103"/>
-    </row>
-    <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="101" t="s">
+      <c r="G12" s="104"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="104"/>
+    </row>
+    <row r="13" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="110" t="s">
         <v>361</v>
       </c>
-      <c r="C13" s="101" t="s">
+      <c r="C13" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="102" t="s">
+      <c r="D13" s="110" t="s">
         <v>418</v>
       </c>
-      <c r="E13" s="101" t="s">
+      <c r="E13" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="102" t="s">
+      <c r="F13" s="103" t="s">
         <v>340</v>
       </c>
-      <c r="G13" s="103"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="103"/>
-    </row>
-    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="101" t="s">
+      <c r="G13" s="104"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="104"/>
+    </row>
+    <row r="14" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="110" t="s">
         <v>362</v>
       </c>
-      <c r="C14" s="101" t="s">
+      <c r="C14" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="102" t="s">
+      <c r="D14" s="110" t="s">
         <v>393</v>
       </c>
-      <c r="E14" s="101" t="s">
+      <c r="E14" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="102" t="s">
+      <c r="F14" s="103" t="s">
         <v>340</v>
       </c>
-      <c r="G14" s="103"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="103"/>
-    </row>
-    <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="101" t="s">
+      <c r="G14" s="104"/>
+      <c r="H14" s="106"/>
+      <c r="I14" s="104"/>
+    </row>
+    <row r="15" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="102" t="s">
         <v>331</v>
       </c>
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="110" t="s">
         <v>363</v>
       </c>
-      <c r="C15" s="101" t="s">
+      <c r="C15" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="102" t="s">
+      <c r="D15" s="110" t="s">
         <v>394</v>
       </c>
-      <c r="E15" s="101" t="s">
+      <c r="E15" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="102" t="s">
+      <c r="F15" s="103" t="s">
         <v>341</v>
       </c>
-      <c r="G15" s="103"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="103"/>
-    </row>
-    <row r="16" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="101" t="s">
+      <c r="G15" s="104"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="104"/>
+    </row>
+    <row r="16" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="110" t="s">
         <v>364</v>
       </c>
-      <c r="C16" s="101" t="s">
+      <c r="C16" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="102" t="s">
+      <c r="D16" s="110" t="s">
         <v>395</v>
       </c>
-      <c r="E16" s="101" t="s">
+      <c r="E16" s="102" t="s">
         <v>299</v>
       </c>
-      <c r="F16" s="102" t="s">
+      <c r="F16" s="103" t="s">
         <v>342</v>
       </c>
-      <c r="G16" s="103"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="103"/>
-    </row>
-    <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="101" t="s">
+      <c r="G16" s="104"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="104"/>
+    </row>
+    <row r="17" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="102" t="s">
+      <c r="B17" s="110" t="s">
         <v>365</v>
       </c>
-      <c r="C17" s="101" t="s">
+      <c r="C17" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="102" t="s">
+      <c r="D17" s="110" t="s">
         <v>396</v>
       </c>
-      <c r="E17" s="101" t="s">
+      <c r="E17" s="102" t="s">
         <v>282</v>
       </c>
-      <c r="F17" s="102" t="s">
+      <c r="F17" s="103" t="s">
         <v>342</v>
       </c>
-      <c r="G17" s="103"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="103"/>
-    </row>
-    <row r="18" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="101" t="s">
+      <c r="G17" s="104"/>
+      <c r="H17" s="105"/>
+      <c r="I17" s="104"/>
+    </row>
+    <row r="18" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="102" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="102" t="s">
+      <c r="B18" s="110" t="s">
         <v>366</v>
       </c>
-      <c r="C18" s="101" t="s">
+      <c r="C18" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="102" t="s">
+      <c r="D18" s="110" t="s">
         <v>397</v>
       </c>
-      <c r="E18" s="101" t="s">
+      <c r="E18" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="102" t="s">
+      <c r="F18" s="103" t="s">
         <v>281</v>
       </c>
-      <c r="G18" s="103"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="103"/>
-    </row>
-    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="101" t="s">
+      <c r="G18" s="104"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="104"/>
+    </row>
+    <row r="19" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="102" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="102" t="s">
+      <c r="B19" s="110" t="s">
         <v>367</v>
       </c>
-      <c r="C19" s="101" t="s">
+      <c r="C19" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="102" t="s">
+      <c r="D19" s="110" t="s">
         <v>398</v>
       </c>
-      <c r="E19" s="101" t="s">
+      <c r="E19" s="102" t="s">
         <v>276</v>
       </c>
-      <c r="F19" s="102" t="s">
+      <c r="F19" s="103" t="s">
         <v>343</v>
       </c>
-      <c r="G19" s="103"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="103"/>
-    </row>
-    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="101" t="s">
+      <c r="G19" s="104"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="104"/>
+    </row>
+    <row r="20" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="102" t="s">
+      <c r="B20" s="110" t="s">
         <v>368</v>
       </c>
-      <c r="C20" s="101" t="s">
+      <c r="C20" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="102" t="s">
+      <c r="D20" s="110" t="s">
         <v>399</v>
       </c>
-      <c r="E20" s="101" t="s">
+      <c r="E20" s="102" t="s">
         <v>277</v>
       </c>
-      <c r="F20" s="102" t="s">
+      <c r="F20" s="103" t="s">
         <v>344</v>
       </c>
-      <c r="G20" s="103"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="103"/>
-    </row>
-    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="101" t="s">
+      <c r="G20" s="104"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="104"/>
+    </row>
+    <row r="21" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="102" t="s">
+      <c r="B21" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="C21" s="101" t="s">
+      <c r="C21" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="102" t="s">
+      <c r="D21" s="110" t="s">
         <v>400</v>
       </c>
-      <c r="E21" s="101" t="s">
+      <c r="E21" s="102" t="s">
         <v>283</v>
       </c>
-      <c r="F21" s="102" t="s">
+      <c r="F21" s="103" t="s">
         <v>343</v>
       </c>
-      <c r="G21" s="103"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="103"/>
-    </row>
-    <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="101" t="s">
+      <c r="G21" s="104"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="104"/>
+    </row>
+    <row r="22" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A22" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="102" t="s">
+      <c r="B22" s="110" t="s">
         <v>370</v>
       </c>
-      <c r="C22" s="101" t="s">
+      <c r="C22" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="102" t="s">
+      <c r="D22" s="110" t="s">
         <v>401</v>
       </c>
-      <c r="E22" s="101" t="s">
+      <c r="E22" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="102" t="s">
+      <c r="F22" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="G22" s="103"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="103"/>
-    </row>
-    <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="101" t="s">
+      <c r="G22" s="104"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="104"/>
+    </row>
+    <row r="23" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A23" s="102" t="s">
         <v>315</v>
       </c>
-      <c r="B23" s="102" t="s">
+      <c r="B23" s="110" t="s">
         <v>371</v>
       </c>
-      <c r="C23" s="101" t="s">
+      <c r="C23" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="102" t="s">
+      <c r="D23" s="110" t="s">
         <v>402</v>
       </c>
-      <c r="E23" s="103"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="101" t="s">
+      <c r="E23" s="104"/>
+      <c r="F23" s="106"/>
+    </row>
+    <row r="24" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="102" t="s">
         <v>330</v>
       </c>
-      <c r="B24" s="102" t="s">
+      <c r="B24" s="110" t="s">
         <v>372</v>
       </c>
-      <c r="C24" s="101" t="s">
+      <c r="C24" s="102" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="102" t="s">
+      <c r="D24" s="110" t="s">
         <v>403</v>
       </c>
-      <c r="E24" s="103"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="101" t="s">
+      <c r="E24" s="104"/>
+      <c r="F24" s="106"/>
+    </row>
+    <row r="25" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="102" t="s">
+      <c r="B25" s="110" t="s">
         <v>373</v>
       </c>
-      <c r="C25" s="101" t="s">
+      <c r="C25" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="102" t="s">
+      <c r="D25" s="110" t="s">
         <v>404</v>
       </c>
-      <c r="E25" s="103"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="101" t="s">
+      <c r="E25" s="104"/>
+      <c r="F25" s="106"/>
+    </row>
+    <row r="26" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A26" s="102" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="102" t="s">
+      <c r="B26" s="110" t="s">
         <v>374</v>
       </c>
-      <c r="C26" s="101" t="s">
+      <c r="C26" s="102" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="102" t="s">
+      <c r="D26" s="110" t="s">
         <v>405</v>
       </c>
-      <c r="E26" s="103"/>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="101" t="s">
+      <c r="E26" s="104"/>
+      <c r="F26" s="106"/>
+    </row>
+    <row r="27" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A27" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="102" t="s">
+      <c r="B27" s="110" t="s">
         <v>375</v>
       </c>
-      <c r="C27" s="101" t="s">
+      <c r="C27" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="102" t="s">
+      <c r="D27" s="110" t="s">
         <v>406</v>
       </c>
-      <c r="E27" s="103"/>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="101" t="s">
+      <c r="E27" s="104"/>
+      <c r="F27" s="106"/>
+    </row>
+    <row r="28" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="102" t="s">
+      <c r="B28" s="110" t="s">
         <v>376</v>
       </c>
-      <c r="C28" s="101" t="s">
+      <c r="C28" s="102" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="102" t="s">
+      <c r="D28" s="110" t="s">
         <v>407</v>
       </c>
-      <c r="E28" s="103"/>
-      <c r="F28" s="3"/>
-    </row>
-    <row r="29" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="101" t="s">
+      <c r="E28" s="104"/>
+      <c r="F28" s="106"/>
+    </row>
+    <row r="29" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="102" t="s">
+      <c r="B29" s="110" t="s">
         <v>377</v>
       </c>
-      <c r="C29" s="101" t="s">
+      <c r="C29" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="102" t="s">
+      <c r="D29" s="110" t="s">
         <v>408</v>
       </c>
-      <c r="E29" s="103"/>
-      <c r="F29" s="3"/>
-    </row>
-    <row r="30" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="101" t="s">
+      <c r="E29" s="104"/>
+      <c r="F29" s="106"/>
+    </row>
+    <row r="30" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A30" s="102" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="102" t="s">
+      <c r="B30" s="110" t="s">
         <v>378</v>
       </c>
-      <c r="C30" s="101" t="s">
+      <c r="C30" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="102" t="s">
+      <c r="D30" s="110" t="s">
         <v>409</v>
       </c>
-      <c r="E30" s="103"/>
-      <c r="F30" s="3"/>
-    </row>
-    <row r="31" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="101" t="s">
+      <c r="E30" s="104"/>
+      <c r="F30" s="106"/>
+    </row>
+    <row r="31" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A31" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="102" t="s">
+      <c r="B31" s="110" t="s">
         <v>379</v>
       </c>
-      <c r="C31" s="101" t="s">
+      <c r="C31" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="D31" s="102" t="s">
+      <c r="D31" s="110" t="s">
         <v>410</v>
       </c>
-      <c r="E31" s="103"/>
-      <c r="F31" s="3"/>
-    </row>
-    <row r="32" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="101" t="s">
+      <c r="E31" s="104"/>
+      <c r="F31" s="106"/>
+    </row>
+    <row r="32" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A32" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="102" t="s">
+      <c r="B32" s="110" t="s">
         <v>380</v>
       </c>
-      <c r="C32" s="104" t="s">
+      <c r="C32" s="107" t="s">
         <v>274</v>
       </c>
-      <c r="D32" s="102" t="s">
+      <c r="D32" s="110" t="s">
         <v>411</v>
       </c>
-      <c r="E32" s="103"/>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="101" t="s">
+      <c r="E32" s="104"/>
+      <c r="F32" s="106"/>
+    </row>
+    <row r="33" spans="1:6" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="102" t="s">
+      <c r="B33" s="110" t="s">
         <v>381</v>
       </c>
-      <c r="C33" s="101" t="s">
+      <c r="C33" s="102" t="s">
         <v>275</v>
       </c>
-      <c r="D33" s="102" t="s">
+      <c r="D33" s="110" t="s">
         <v>412</v>
       </c>
-      <c r="E33" s="103"/>
-      <c r="F33" s="3"/>
-    </row>
-    <row r="34" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="101" t="s">
+      <c r="E33" s="104"/>
+      <c r="F33" s="106"/>
+    </row>
+    <row r="34" spans="1:6" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A34" s="102" t="s">
         <v>257</v>
       </c>
-      <c r="B34" s="102" t="s">
+      <c r="B34" s="110" t="s">
         <v>382</v>
       </c>
-      <c r="C34" s="101" t="s">
+      <c r="C34" s="102" t="s">
         <v>332</v>
       </c>
-      <c r="D34" s="102" t="s">
+      <c r="D34" s="110" t="s">
         <v>413</v>
       </c>
-      <c r="E34" s="103"/>
-      <c r="F34" s="3"/>
-    </row>
-    <row r="35" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="101" t="s">
+      <c r="E34" s="104"/>
+      <c r="F34" s="106"/>
+    </row>
+    <row r="35" spans="1:6" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A35" s="102" t="s">
         <v>266</v>
       </c>
-      <c r="B35" s="102" t="s">
+      <c r="B35" s="110" t="s">
         <v>383</v>
       </c>
-      <c r="C35" s="101" t="s">
+      <c r="C35" s="102" t="s">
         <v>333</v>
       </c>
-      <c r="D35" s="102" t="s">
+      <c r="D35" s="110" t="s">
         <v>414</v>
       </c>
-      <c r="E35" s="103"/>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="101" t="s">
+      <c r="E35" s="104"/>
+      <c r="F35" s="106"/>
+    </row>
+    <row r="36" spans="1:6" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A36" s="102" t="s">
         <v>312</v>
       </c>
-      <c r="B36" s="102" t="s">
+      <c r="B36" s="110" t="s">
         <v>384</v>
       </c>
-      <c r="C36" s="103"/>
+      <c r="C36" s="104"/>
       <c r="D36" s="3"/>
-      <c r="E36" s="103"/>
-    </row>
-    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="101" t="s">
+      <c r="E36" s="104"/>
+    </row>
+    <row r="37" spans="1:6" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A37" s="102" t="s">
         <v>273</v>
       </c>
-      <c r="B37" s="102" t="s">
+      <c r="B37" s="110" t="s">
         <v>385</v>
       </c>
-      <c r="C37" s="103"/>
+      <c r="C37" s="104"/>
       <c r="D37" s="3"/>
-      <c r="E37" s="103"/>
-    </row>
-    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="101" t="s">
+      <c r="E37" s="104"/>
+    </row>
+    <row r="38" spans="1:6" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A38" s="102" t="s">
         <v>279</v>
       </c>
-      <c r="B38" s="102" t="s">
+      <c r="B38" s="110" t="s">
         <v>386</v>
       </c>
-      <c r="C38" s="103"/>
+      <c r="C38" s="104"/>
       <c r="D38" s="3"/>
-      <c r="E38" s="103"/>
-    </row>
-    <row r="39" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="101" t="s">
+      <c r="E38" s="104"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="102" t="s">
         <v>290</v>
       </c>
-      <c r="B39" s="102" t="s">
+      <c r="B39" s="110" t="s">
         <v>387</v>
       </c>
-      <c r="C39" s="103"/>
+      <c r="C39" s="104"/>
       <c r="D39" s="3"/>
-      <c r="E39" s="103"/>
+      <c r="E39" s="104"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4427,20 +4437,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D195C1D-DB02-1743-BBD2-99104C1FFD33}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.71875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" customWidth="1"/>
+    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.55859375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.26171875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.7890625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.16796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.0859375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>68</v>
       </c>
@@ -4469,7 +4479,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>217</v>
       </c>
@@ -4498,7 +4508,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>236</v>
       </c>
@@ -4527,7 +4537,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="81" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>86</v>
       </c>
@@ -4554,7 +4564,7 @@
       </c>
       <c r="I4" s="19"/>
     </row>
-    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>92</v>
       </c>
@@ -4581,7 +4591,7 @@
       </c>
       <c r="I5" s="19"/>
     </row>
-    <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="108" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>96</v>
       </c>
@@ -4608,7 +4618,7 @@
       </c>
       <c r="I6" s="19"/>
     </row>
-    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>101</v>
       </c>
@@ -4633,7 +4643,7 @@
       <c r="H7" s="16"/>
       <c r="I7" s="19"/>
     </row>
-    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>104</v>
       </c>
@@ -4656,7 +4666,7 @@
       <c r="H8" s="16"/>
       <c r="I8" s="19"/>
     </row>
-    <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="108" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>108</v>
       </c>
@@ -4679,7 +4689,7 @@
       <c r="H9" s="16"/>
       <c r="I9" s="19"/>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>327</v>
       </c>
@@ -4700,7 +4710,7 @@
       <c r="H10" s="16"/>
       <c r="I10" s="19"/>
     </row>
-    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>115</v>
       </c>
@@ -4719,7 +4729,7 @@
       <c r="H11" s="16"/>
       <c r="I11" s="19"/>
     </row>
-    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>116</v>
       </c>
@@ -4738,7 +4748,7 @@
       <c r="H12" s="16"/>
       <c r="I12" s="19"/>
     </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>119</v>
       </c>
@@ -4757,7 +4767,7 @@
       <c r="H13" s="16"/>
       <c r="I13" s="19"/>
     </row>
-    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>122</v>
       </c>
@@ -4776,7 +4786,7 @@
       <c r="H14" s="16"/>
       <c r="I14" s="19"/>
     </row>
-    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>126</v>
       </c>
@@ -4793,7 +4803,7 @@
       <c r="H15" s="16"/>
       <c r="I15" s="19"/>
     </row>
-    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>128</v>
       </c>
@@ -4810,7 +4820,7 @@
       <c r="H16" s="16"/>
       <c r="I16" s="19"/>
     </row>
-    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>270</v>
       </c>
@@ -4827,7 +4837,7 @@
       <c r="H17" s="16"/>
       <c r="I17" s="19"/>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>130</v>
       </c>
@@ -4844,7 +4854,7 @@
       <c r="H18" s="16"/>
       <c r="I18" s="19"/>
     </row>
-    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>133</v>
       </c>
@@ -4861,7 +4871,7 @@
       <c r="H19" s="16"/>
       <c r="I19" s="19"/>
     </row>
-    <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>135</v>
       </c>
@@ -4878,7 +4888,7 @@
       <c r="H20" s="16"/>
       <c r="I20" s="19"/>
     </row>
-    <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>255</v>
       </c>
@@ -4895,7 +4905,7 @@
       <c r="H21" s="16"/>
       <c r="I21" s="19"/>
     </row>
-    <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
         <v>122</v>
       </c>
@@ -4912,7 +4922,7 @@
       <c r="H22" s="16"/>
       <c r="I22" s="19"/>
     </row>
-    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>126</v>
       </c>
@@ -4929,7 +4939,7 @@
       <c r="H23" s="16"/>
       <c r="I23" s="19"/>
     </row>
-    <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>128</v>
       </c>
@@ -4946,7 +4956,7 @@
       <c r="H24" s="16"/>
       <c r="I24" s="19"/>
     </row>
-    <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>270</v>
       </c>
@@ -4972,13 +4982,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920DF489-FE6D-4819-BD1A-323DFAE597A3}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="30.66796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="39"/>
       <c r="B1" s="33" t="s">
         <v>140</v>
@@ -5002,7 +5012,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="41" t="s">
         <v>146</v>
       </c>
@@ -5028,7 +5038,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="41" t="s">
         <v>147</v>
       </c>
@@ -5054,7 +5064,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="41" t="s">
         <v>148</v>
       </c>
@@ -5080,7 +5090,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
         <v>149</v>
       </c>
@@ -5106,7 +5116,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="64" t="s">
         <v>150</v>
       </c>
@@ -5132,7 +5142,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="44" t="s">
         <v>151</v>
       </c>
@@ -5158,7 +5168,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="62" t="s">
         <v>200</v>
       </c>
@@ -5184,7 +5194,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="31" t="s">
         <v>201</v>
       </c>
@@ -5207,7 +5217,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="63" t="s">
         <v>202</v>
       </c>
@@ -5230,12 +5240,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>226</v>
       </c>
@@ -5258,7 +5268,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
         <v>205</v>
@@ -5279,7 +5289,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
         <v>321</v>
@@ -5300,7 +5310,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
         <v>324</v>
@@ -5321,7 +5331,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -5330,7 +5340,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>227</v>
       </c>
@@ -5356,7 +5366,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
         <v>327</v>
@@ -5380,7 +5390,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
         <v>205</v>
@@ -5401,7 +5411,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
@@ -5420,7 +5430,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
       <c r="B22" s="2"/>
       <c r="D22" s="2" t="s">
@@ -5428,7 +5438,7 @@
       </c>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
       <c r="B23" s="2"/>
       <c r="D23" s="2"/>
@@ -5436,7 +5446,7 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>228</v>
       </c>
@@ -5462,7 +5472,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
         <v>116</v>
@@ -5486,7 +5496,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
         <v>296</v>
@@ -5510,7 +5520,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
@@ -5527,7 +5537,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -5539,7 +5549,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -5551,7 +5561,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -5560,7 +5570,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -5568,7 +5578,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -5576,7 +5586,7 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -5584,7 +5594,7 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -5592,7 +5602,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -5600,7 +5610,7 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -5608,7 +5618,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -5616,7 +5626,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -5624,7 +5634,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -5632,7 +5642,7 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -5640,7 +5650,7 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -5648,7 +5658,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -5656,7 +5666,7 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -5664,7 +5674,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -5672,7 +5682,7 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="3"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -5680,7 +5690,7 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -5694,21 +5704,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4430D7D8-35BC-4E32-9DE8-E2E435ADAAA0}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="36" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="37.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="6" width="30.7109375" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="6" width="30.66796875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="9.14453125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="114" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="111"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="116"/>
     </row>
     <row r="2" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="99" t="s">
@@ -5837,11 +5847,11 @@
       <c r="B8" s="76" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="106" t="s">
+      <c r="C8" s="111" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="107"/>
-      <c r="E8" s="108"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="113"/>
       <c r="F8" s="96">
         <v>10</v>
       </c>
@@ -5920,66 +5930,66 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CEB427C-0CB4-4E8D-8367-36F6DD891282}">
   <dimension ref="A1:CA6"/>
-  <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.7734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" style="31"/>
-    <col min="2" max="2" width="19.7109375" style="43"/>
-    <col min="4" max="4" width="19.7109375" style="31"/>
-    <col min="6" max="6" width="19.7109375" style="31"/>
-    <col min="8" max="8" width="19.7109375" style="31"/>
-    <col min="10" max="10" width="19.7109375" style="31"/>
-    <col min="12" max="12" width="19.7109375" style="31"/>
-    <col min="14" max="14" width="19.7109375" style="31"/>
-    <col min="16" max="16" width="19.7109375" style="31"/>
-    <col min="18" max="18" width="19.7109375" style="31"/>
-    <col min="20" max="20" width="19.7109375" style="31"/>
-    <col min="22" max="22" width="19.7109375" style="31"/>
-    <col min="24" max="24" width="19.7109375" style="31"/>
-    <col min="26" max="26" width="19.7109375" style="31"/>
-    <col min="28" max="28" width="19.7109375" style="31"/>
-    <col min="30" max="30" width="19.7109375" style="49"/>
-    <col min="31" max="32" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.7109375" customWidth="1"/>
-    <col min="42" max="42" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.7109375" style="49" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="19.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="19.7109375" style="49" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="19.7109375" style="31"/>
-    <col min="63" max="63" width="19.7109375" style="31"/>
-    <col min="65" max="65" width="19.7109375" style="31"/>
-    <col min="67" max="67" width="19.7109375" style="31"/>
-    <col min="69" max="70" width="19.7109375" style="31"/>
-    <col min="71" max="71" width="19.7109375" style="43"/>
-    <col min="73" max="73" width="19.7109375" style="31"/>
-    <col min="75" max="75" width="19.7109375" style="31"/>
-    <col min="77" max="77" width="19.7109375" style="31"/>
-    <col min="79" max="79" width="19.7109375" style="31"/>
+    <col min="1" max="1" width="19.7734375" style="31"/>
+    <col min="2" max="2" width="19.7734375" style="43"/>
+    <col min="4" max="4" width="19.7734375" style="31"/>
+    <col min="6" max="6" width="19.7734375" style="31"/>
+    <col min="8" max="8" width="19.7734375" style="31"/>
+    <col min="10" max="10" width="19.7734375" style="31"/>
+    <col min="12" max="12" width="19.7734375" style="31"/>
+    <col min="14" max="14" width="19.7734375" style="31"/>
+    <col min="16" max="16" width="19.7734375" style="31"/>
+    <col min="18" max="18" width="19.7734375" style="31"/>
+    <col min="20" max="20" width="19.7734375" style="31"/>
+    <col min="22" max="22" width="19.7734375" style="31"/>
+    <col min="24" max="24" width="19.7734375" style="31"/>
+    <col min="26" max="26" width="19.7734375" style="31"/>
+    <col min="28" max="28" width="19.7734375" style="31"/>
+    <col min="30" max="30" width="19.7734375" style="49"/>
+    <col min="31" max="32" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.7734375" customWidth="1"/>
+    <col min="42" max="42" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.7734375" style="49" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="19.7734375" style="31" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19.7734375" style="49" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="19.7734375" style="31"/>
+    <col min="63" max="63" width="19.7734375" style="31"/>
+    <col min="65" max="65" width="19.7734375" style="31"/>
+    <col min="67" max="67" width="19.7734375" style="31"/>
+    <col min="69" max="70" width="19.7734375" style="31"/>
+    <col min="71" max="71" width="19.7734375" style="43"/>
+    <col min="73" max="73" width="19.7734375" style="31"/>
+    <col min="75" max="75" width="19.7734375" style="31"/>
+    <col min="77" max="77" width="19.7734375" style="31"/>
+    <col min="79" max="79" width="19.7734375" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" s="47" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:79" s="47" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="45" t="str">
         <f>Cards!A2</f>
         <v>Fillibuster</v>
@@ -6266,7 +6276,7 @@
       <c r="BY1" s="45"/>
       <c r="CA1" s="45"/>
     </row>
-    <row r="2" spans="1:79" s="70" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:79" s="70" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="e">
         <f>Cards!#REF!</f>
         <v>#REF!</v>
@@ -6553,7 +6563,7 @@
       <c r="BY2" s="71"/>
       <c r="CA2" s="71"/>
     </row>
-    <row r="3" spans="1:79" s="47" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:79" s="47" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="45" t="str">
         <f>Cards!C2</f>
         <v>Full Coffers</v>
@@ -6837,7 +6847,7 @@
       <c r="BY3" s="45"/>
       <c r="CA3" s="45"/>
     </row>
-    <row r="4" spans="1:79" s="52" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:79" s="52" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="e">
         <f>Cards!#REF!</f>
         <v>#REF!</v>
@@ -7121,7 +7131,7 @@
       <c r="BY4" s="50"/>
       <c r="CA4" s="50"/>
     </row>
-    <row r="5" spans="1:79" s="56" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:79" s="56" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="54" t="str">
         <f>Cards!E2</f>
         <v>Fickle Mercenaries</v>
@@ -7401,7 +7411,7 @@
       <c r="BY5" s="54"/>
       <c r="CA5" s="54"/>
     </row>
-    <row r="6" spans="1:79" s="52" customFormat="1" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:79" s="52" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="50" t="e">
         <f>Cards!#REF!</f>
         <v>#REF!</v>
@@ -7690,16 +7700,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BDA35E-BFC3-134A-A064-89D65A8B31CF}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.50390625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.22265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>178</v>
       </c>
@@ -7716,7 +7726,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>159</v>
       </c>
@@ -7731,7 +7741,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>160</v>
       </c>
@@ -7746,7 +7756,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>161</v>
       </c>
@@ -7761,7 +7771,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>162</v>
       </c>
@@ -7773,7 +7783,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>174</v>
       </c>
@@ -7788,7 +7798,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>163</v>
       </c>
@@ -7803,7 +7813,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>164</v>
       </c>
@@ -7818,7 +7828,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>165</v>
       </c>
@@ -7833,7 +7843,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>166</v>
       </c>
@@ -7848,7 +7858,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>167</v>
       </c>
@@ -7863,7 +7873,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>168</v>
       </c>
@@ -7878,7 +7888,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>169</v>
       </c>
@@ -7893,7 +7903,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>170</v>
       </c>
@@ -7904,7 +7914,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>171</v>
       </c>
@@ -7915,7 +7925,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>172</v>
       </c>
@@ -7926,7 +7936,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>173</v>
       </c>
@@ -7937,7 +7947,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>177</v>
       </c>
@@ -7949,7 +7959,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>176</v>
       </c>
@@ -7961,7 +7971,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>175</v>
       </c>
@@ -7973,7 +7983,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>188</v>
       </c>
@@ -7993,24 +8003,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC83F89-2724-CA43-A519-59213A612B31}">
   <dimension ref="A1:U55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24" style="73" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.42578125" style="75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="75" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="11.85546875" style="75" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" style="75" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.9609375" style="73" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.72265625" customWidth="1"/>
+    <col min="4" max="4" width="8.33984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.27734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.43359375" style="75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.22265625" style="75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.43359375" style="75" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="11.8359375" style="75" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.9140625" style="75" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>237</v>
       </c>
@@ -8075,7 +8085,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="73">
         <v>46075</v>
       </c>
@@ -8119,7 +8129,7 @@
         <v>0.92638888888888893</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="73">
         <v>46089</v>
       </c>
@@ -8175,7 +8185,7 @@
         <v>0.86527777777777781</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="73">
         <v>46105</v>
       </c>
@@ -8228,7 +8238,7 @@
         <v>0.92777777777777781</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="73">
         <v>46118</v>
       </c>
@@ -8281,7 +8291,7 @@
         <v>0.9194444444444444</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="73">
         <v>46124</v>
       </c>
@@ -8325,7 +8335,7 @@
         <v>0.74583333333333335</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="73">
         <v>46131</v>
       </c>
@@ -8378,7 +8388,7 @@
         <v>0.70277777777777772</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="73">
         <v>46138</v>
       </c>
@@ -8422,7 +8432,7 @@
         <v>0.69513888888888886</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="73">
         <v>46145</v>
       </c>
@@ -8475,7 +8485,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="73">
         <v>46152</v>
       </c>
@@ -8525,7 +8535,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="73">
         <v>46158</v>
       </c>
@@ -8578,7 +8588,7 @@
         <v>0.99236111111111114</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="73">
         <v>46215</v>
       </c>
@@ -8637,7 +8647,7 @@
         <v>0.73888888888888893</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="73">
         <v>46247</v>
       </c>
@@ -8690,15 +8700,63 @@
         <v>0.9458333333333333</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" s="73">
+        <v>46277</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
       <c r="C14" s="74" t="b">
         <v>0</v>
       </c>
       <c r="D14" s="74" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>16</v>
+      </c>
+      <c r="F14">
+        <v>21</v>
+      </c>
+      <c r="G14">
+        <v>13</v>
+      </c>
+      <c r="H14" s="75">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="I14" s="75">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="J14" s="75">
+        <v>0.80902777777777779</v>
+      </c>
+      <c r="K14" s="75">
+        <v>0.81736111111111109</v>
+      </c>
+      <c r="L14" s="75">
+        <v>0.8354166666666667</v>
+      </c>
+      <c r="M14" s="75">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N14" s="75">
+        <v>0.86736111111111114</v>
+      </c>
+      <c r="O14" s="75">
+        <v>0.88749999999999996</v>
+      </c>
+      <c r="P14" s="75">
+        <v>0.90138888888888891</v>
+      </c>
+      <c r="Q14" s="75">
+        <v>0.92013888888888884</v>
+      </c>
+      <c r="U14" s="75">
+        <v>0.92500000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="74" t="b">
         <v>0</v>
       </c>
@@ -8706,7 +8764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C16" s="74" t="b">
         <v>0</v>
       </c>
@@ -8714,7 +8772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C17" s="74" t="b">
         <v>0</v>
       </c>
@@ -8722,7 +8780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C18" s="74" t="b">
         <v>0</v>
       </c>
@@ -8730,7 +8788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C19" s="74" t="b">
         <v>0</v>
       </c>
@@ -8738,7 +8796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C20" s="74" t="b">
         <v>0</v>
       </c>
@@ -8746,7 +8804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C21" s="74" t="b">
         <v>0</v>
       </c>
@@ -8754,7 +8812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C22" s="74" t="b">
         <v>0</v>
       </c>
@@ -8762,7 +8820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C23" s="74" t="b">
         <v>0</v>
       </c>
@@ -8770,7 +8828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C24" s="74" t="b">
         <v>0</v>
       </c>
@@ -8778,7 +8836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C25" s="74" t="b">
         <v>0</v>
       </c>
@@ -8786,7 +8844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C26" s="74" t="b">
         <v>0</v>
       </c>
@@ -8794,7 +8852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C27" s="74" t="b">
         <v>0</v>
       </c>
@@ -8802,7 +8860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C28" s="74" t="b">
         <v>0</v>
       </c>
@@ -8810,7 +8868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C29" s="74" t="b">
         <v>0</v>
       </c>
@@ -8818,7 +8876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C30" s="74" t="b">
         <v>0</v>
       </c>
@@ -8826,7 +8884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C31" s="74" t="b">
         <v>0</v>
       </c>
@@ -8834,7 +8892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C32" s="74" t="b">
         <v>0</v>
       </c>
@@ -8842,7 +8900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C33" s="74" t="b">
         <v>0</v>
       </c>
@@ -8850,7 +8908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C34" s="74" t="b">
         <v>0</v>
       </c>
@@ -8858,7 +8916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C35" s="74" t="b">
         <v>0</v>
       </c>
@@ -8866,7 +8924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C36" s="74" t="b">
         <v>0</v>
       </c>
@@ -8874,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C37" s="74" t="b">
         <v>0</v>
       </c>
@@ -8882,7 +8940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C38" s="74" t="b">
         <v>0</v>
       </c>
@@ -8890,7 +8948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C39" s="74" t="b">
         <v>0</v>
       </c>
@@ -8898,7 +8956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C40" s="74" t="b">
         <v>0</v>
       </c>
@@ -8906,7 +8964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C41" s="74" t="b">
         <v>0</v>
       </c>
@@ -8914,7 +8972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C42" s="74" t="b">
         <v>0</v>
       </c>
@@ -8922,7 +8980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C43" s="74" t="b">
         <v>0</v>
       </c>
@@ -8930,7 +8988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C44" s="74" t="b">
         <v>0</v>
       </c>
@@ -8938,7 +8996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C45" s="74" t="b">
         <v>0</v>
       </c>
@@ -8946,7 +9004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C46" s="74" t="b">
         <v>0</v>
       </c>
@@ -8954,7 +9012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C47" s="74" t="b">
         <v>0</v>
       </c>
@@ -8962,7 +9020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C48" s="74" t="b">
         <v>0</v>
       </c>
@@ -8970,7 +9028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C49" s="74" t="b">
         <v>0</v>
       </c>
@@ -8978,7 +9036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C50" s="74" t="b">
         <v>0</v>
       </c>
@@ -8986,7 +9044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C51" s="74" t="b">
         <v>0</v>
       </c>
@@ -8994,7 +9052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C52" s="74" t="b">
         <v>0</v>
       </c>
@@ -9002,7 +9060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C53" s="74" t="b">
         <v>0</v>
       </c>
@@ -9010,7 +9068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C54" s="74" t="b">
         <v>0</v>
       </c>
@@ -9018,7 +9076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C55" s="74" t="b">
         <v>0</v>
       </c>

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4709" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43E468BA-BB90-408B-BE7A-5A8C3FE17CC2}"/>
+  <xr:revisionPtr revIDLastSave="4739" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F7C9001-ABB5-474D-8310-7CB85E30C8A9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -670,94 +670,94 @@
     <t>Law HTML Description</t>
   </si>
   <si>
-    <t>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</t>
-  </si>
-  <si>
-    <t>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</t>
-  </si>
-  <si>
-    <t>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Commission</t>
-  </si>
-  <si>
-    <t>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Commission</t>
-  </si>
-  <si>
-    <t>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition</t>
-  </si>
-  <si>
-    <t>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition</t>
-  </si>
-  <si>
-    <t>Each Player must have at least $L6 sponsored Laws in the Edicts or in the Queue or they will suffer sanctions on Tax</t>
-  </si>
-  <si>
-    <t>No Player may have more than $L6 sponsored Laws in the Edicts or in the queue or they will suffer sanctions on Tax</t>
-  </si>
-  <si>
-    <t>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</t>
-  </si>
-  <si>
-    <t>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</t>
-  </si>
-  <si>
-    <t>Each Player must Collect at least $L6 Commodities this round or they will suffer sanctions on Recruit</t>
-  </si>
-  <si>
-    <t>No Player may Collect more than $L6 Commodities this round or they will suffer sanctions on Recruit</t>
-  </si>
-  <si>
-    <t>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</t>
-  </si>
-  <si>
-    <t>No Player may have more than 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</t>
-  </si>
-  <si>
-    <t>Each Player must have at least $L6 Troops or they will suffer sanctions on Collect</t>
-  </si>
-  <si>
-    <t>No Player may have more than $L6 Troops or they will suffer sanctions on Collect</t>
-  </si>
-  <si>
-    <t>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</t>
-  </si>
-  <si>
-    <t>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</t>
-  </si>
-  <si>
-    <t>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</t>
-  </si>
-  <si>
-    <t>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</t>
-  </si>
-  <si>
-    <t>Each Player must have at least $L6 Cards of each type in hand or they will suffer sanctions on Monetize</t>
-  </si>
-  <si>
-    <t>No Player may have more than $L6 Cards of each type in their hand or they will suffer sanctions on Monetize</t>
-  </si>
-  <si>
-    <t>Each Player must Deploy at least $L6 Troops or they will suffer sanctions on Donate</t>
-  </si>
-  <si>
-    <t>No Player may Deploy more than $L6 Troops or they will suffer sanctions on Donate</t>
-  </si>
-  <si>
-    <t>Each Player must Donate at least $L6 Coins or they will suffer sanctions on Postpone &amp; Prioritize</t>
-  </si>
-  <si>
-    <t>No Player may Donate more than $L6 Coins or they will suffer sanctions on Postpone &amp; Prioritize</t>
-  </si>
-  <si>
-    <t>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy</t>
-  </si>
-  <si>
-    <t>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy</t>
-  </si>
-  <si>
-    <t>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</t>
-  </si>
-  <si>
-    <t>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</t>
+    <t>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions</t>
+  </si>
+  <si>
+    <t>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may have more than 3 + $L6 Investments or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must have an Investment with at least level $L6 or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may have an Investment higher than level $L6 or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must deploy at least $L6 Troops or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may deploy more than $L6 Troops or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must have at least $L6 sponsored Laws in the Edicts or in the Queue or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may have more than $L6 sponsored Laws in the Edicts or in the queue or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must have a Leader with at least level $L6 or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may have a Leader higher than level $L6 or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must Collect at least $L6 Commodities this round or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may Collect more than $L6 Commodities this round or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may have more than 3 + $L6 Leaders or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must have at least $L6 Troops or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may have more than $L6 Troops or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions</t>
+  </si>
+  <si>
+    <t>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions</t>
+  </si>
+  <si>
+    <t>At least $L6 Players must use Court Actions or all Players suffer sanctions</t>
+  </si>
+  <si>
+    <t>No more than $L6 Players may use Court Actions or all Players suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must have at least $L6 Cards of each type in hand or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may have more than $L6 Cards of each type in their hand or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must Deploy at least $L6 Troops or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may Deploy more than $L6 Troops or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>Each Player must Donate at least $L6 Coins or they will suffer sanctions</t>
+  </si>
+  <si>
+    <t>No Player may Donate more than $L6 Coins or they will suffer sanctions</t>
   </si>
 </sst>
 </file>
@@ -877,6 +877,10 @@
     </a>
   </bag>
 </FeaturePropertyBags>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1261,7 +1265,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="10"/>
     </row>
-    <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>117</v>
       </c>
@@ -1433,7 +1437,7 @@
         <v>148</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>141</v>
@@ -1456,7 +1460,7 @@
         <v>23</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>145</v>
@@ -1479,7 +1483,7 @@
         <v>26</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>24</v>
@@ -1502,7 +1506,7 @@
         <v>28</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>27</v>
@@ -1514,7 +1518,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="10"/>
     </row>
-    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>34</v>
       </c>
@@ -1525,7 +1529,7 @@
         <v>30</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>22</v>
@@ -1537,7 +1541,7 @@
       <c r="H14" s="3"/>
       <c r="I14" s="10"/>
     </row>
-    <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>152</v>
       </c>
@@ -1548,7 +1552,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>33</v>
@@ -1560,7 +1564,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="10"/>
     </row>
-    <row r="16" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>36</v>
       </c>
@@ -1571,7 +1575,7 @@
         <v>35</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>134</v>
@@ -1583,7 +1587,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="10"/>
     </row>
-    <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>39</v>
       </c>
@@ -1594,7 +1598,7 @@
         <v>37</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>131</v>
@@ -1617,7 +1621,7 @@
         <v>38</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>19</v>
@@ -1640,7 +1644,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>127</v>
@@ -1663,7 +1667,7 @@
         <v>42</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>128</v>
@@ -1686,7 +1690,7 @@
         <v>44</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>132</v>
@@ -1709,7 +1713,7 @@
         <v>46</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>16</v>
@@ -1721,7 +1725,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="10"/>
     </row>
-    <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>150</v>
       </c>
@@ -1732,12 +1736,12 @@
         <v>48</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>151</v>
       </c>
@@ -1748,12 +1752,12 @@
         <v>50</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E24" s="10"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>53</v>
       </c>
@@ -1764,7 +1768,7 @@
         <v>51</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="3"/>
@@ -1780,7 +1784,7 @@
         <v>52</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="3"/>
@@ -1796,12 +1800,12 @@
         <v>54</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>59</v>
       </c>
@@ -1812,7 +1816,7 @@
         <v>56</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="3"/>
@@ -1828,7 +1832,7 @@
         <v>58</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="3"/>
@@ -1844,7 +1848,7 @@
         <v>60</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="3"/>
@@ -1860,12 +1864,12 @@
         <v>62</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>65</v>
       </c>
@@ -1876,12 +1880,12 @@
         <v>125</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>66</v>
       </c>
@@ -1892,12 +1896,12 @@
         <v>126</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>116</v>
       </c>
@@ -1908,12 +1912,12 @@
         <v>153</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>123</v>
       </c>
@@ -1924,7 +1928,7 @@
         <v>154</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="3"/>
